--- a/SCRAPING-POS--main/Scraping_PyMEs/Base_PyMEs_POS_Providencia.xlsx
+++ b/SCRAPING-POS--main/Scraping_PyMEs/Base_PyMEs_POS_Providencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Groovy</t>
+          <t>Ferretería Ferrealtiro SPA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9 3707 4689</t>
+          <t>9 5371 6712</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Holanda 148, 7500000 Providencia, Región Metropolitana</t>
+          <t>en el tercer pasillo de la Vega Italia - Manuel Montt 1041, Loc 51, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -499,17 +499,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Minimarket El Parque</t>
+          <t>Ferretería Blue XD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9 6796 4702</t>
+          <t>9 9800 0872</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malaquías Concha 0114, 7501547 Providencia, Región Metropolitana</t>
+          <t>Román Díaz 22, 7500607 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -537,17 +537,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Minimarket Comercial Ebenezer</t>
+          <t>Ferretería Yory Providencia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9 5437 8156</t>
+          <t>9 3739 5334</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Av. Tobalaba 4073, 7510734 Providencia, Región Metropolitana</t>
+          <t>Av. Providencia 2349, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -575,17 +575,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Market 360 Spa</t>
+          <t>Ferreteria La Alternativa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9 7465 7775</t>
+          <t>9 5663 9180</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Av. Providencia 1083, 7500608 Providencia, Región Metropolitana</t>
+          <t>Av. Salvador 2328, 7750034 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -613,17 +613,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Go To Mart</t>
+          <t>Ferreteria J Garachena</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9 9883 0642</t>
+          <t>9 3968 0607</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Av. Providencia 2105, 7510121 Santiago, Providencia, Región Metropolitana</t>
+          <t>Av. Francisco Bilbao 3092, 7510716 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -651,17 +651,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria Oriente</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9 3396 4399</t>
+          <t>9 6391 7742</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Regimiento Cazadores 1222, local 6, Providencia, Región Metropolitana</t>
+          <t>Diag. Ote. 1988, 7501351 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -689,17 +689,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Minimarket Ocaranza</t>
+          <t>Puntomak</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9 8831 8402</t>
+          <t>9 5411 6003</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bellavista 0306, 7500000 Providencia, Región Metropolitana</t>
+          <t>Rafael Cañas 192, Ofi 1-A, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -727,17 +727,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Beto market</t>
+          <t>ferrewebmayoristaSpA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Minimarket</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9 7904 4580</t>
+          <t>9 6324 6076</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7500000 Providencia, 7500000 Providencia, Región Metropolitana</t>
+          <t>Av. Providencia 1208, Of. 207, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Almazán</t>
+          <t>Cerrajería 24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9 9434 9563</t>
+          <t>9 8332 8101</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>José Manuel Cousiño 1835, Loc 2, 7510742 Providencia, Región Metropolitana</t>
+          <t>Arzobispo Vicuña 36, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -803,17 +803,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>almacen</t>
+          <t>Guskiner</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Ferreteria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9 9434 9563</t>
+          <t>9 5411 6003</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>José Manuel Cousiño 1835, Loc 2, 7510742 Providencia, Región Metropolitana</t>
+          <t>Rafael Cañas 192, 8320000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -841,17 +841,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Almacén Mi Mordidita</t>
+          <t>S3 Construcciones - Pisos Flotantes y Revestimientos</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Materiales de construccion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9 9302 2542</t>
+          <t>9 9346 0825</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Av. Francisco Bilbao 1189, Loc 1, Providencia, Región Metropolitana</t>
+          <t>Gral. Holley 2294, Piso 3, 7510701 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -879,17 +879,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>El Almacén del Bife</t>
+          <t>Revestimientos y Soluciones Arquitectónicas Matriz SpA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Materiales de construccion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9 9302 2542</t>
+          <t>9 3739 5334</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Av. Francisco Bilbao 1189, Loc 1, Providencia, Región Metropolitana</t>
+          <t>Av. Providencia 2349, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -917,17 +917,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Almacén Animal</t>
+          <t>Taller Mecánico y Mantenciones Valery Cars Providencia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9 9302 2542</t>
+          <t>9 7163 5016</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Av. Francisco Bilbao 1189, Loc 1, Providencia, Región Metropolitana</t>
+          <t>Av. Salvador 1049, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -955,17 +955,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Galería Drugstore</t>
+          <t>AS Automotriz</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9 9302 2542</t>
+          <t>9 9596 6353</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Av. Francisco Bilbao 1189, Loc 1, Providencia, Región Metropolitana</t>
+          <t>Av. Francisco Bilbao 1070, 7501052 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Piwén Metro Pedro de Valdivia</t>
+          <t>Mecanimóvil Mecánicos a Domicilio en Santiago</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9 9302 2542</t>
+          <t>9 9594 5258</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Av. Francisco Bilbao 1189, Loc 1, Providencia, Región Metropolitana</t>
+          <t>Antonio Bellet 193, 7500000 Santiago, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1031,17 +1031,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M3storage Providencia Bodegas y Minibodegas</t>
+          <t>Automotora Sucre</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9 8617 4925</t>
+          <t>9 3532 4999</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Av. Luis Thayer Ojeda 166, 7500000 Providencia, Región Metropolitana</t>
+          <t>José Manuel Infante 1380, 7501256 Providencia, Santiago, Región Metropolitana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1069,17 +1069,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Calper - Uniformes Clínicos Providencia Santiago</t>
+          <t>Servicio Automotriz AGS Ltda.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9 3187 4111</t>
+          <t>9 8229 0203</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Antonio Varas 299, 7500000 Providencia, Región Metropolitana</t>
+          <t>Av. Los Leones 2664, 7511243 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PiedraBruja - Providencia</t>
+          <t>Automotriz Singer y Morales RL Taller Mecanico</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Almacen</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9 7540 3570</t>
+          <t>9 9614 5036</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Av. Providencia 1100, Loc 45, 7500128 Providencia, Región Metropolitana</t>
+          <t>Tegualda 1715, 7750000 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1145,17 +1145,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Botillería Licoreria Nacional</t>
+          <t>Jose Rene Moya Garrido</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9 9952 2064</t>
+          <t>9 8547 7291</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Av. Francisco Bilbao 2383, 7510972 Providencia, Región Metropolitana</t>
+          <t>Julio Prado 1286, 7501301 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Botillería Palamar</t>
+          <t>CarXolutions</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9 4220 5946</t>
+          <t>9 4570 1031</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Av. Providencia 2358, 7510034 Santiago, Providencia, Región Metropolitana</t>
+          <t>Copiapó 757, 8330107 Santiago, Región Metropolitana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1221,17 +1221,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Botillería Moscú Román Díaz</t>
+          <t>Medelauto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9 3956 3062</t>
+          <t>9 4221 4502</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Av. Providencia 1045, 7500620 Providencia, Región Metropolitana</t>
+          <t>Diez de Julio 443, 8330497 Santiago, Región Metropolitana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1259,17 +1259,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Botilleria El Chaguito</t>
+          <t>MANGIARE PIZZERÍA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Taller mecanico</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9 4473 6271</t>
+          <t>9 3245 8957</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manuel Montt 12, Ofi 501, 7500530 Providencia, Región Metropolitana</t>
+          <t>Gerónimo de Alderete 1742, 8241826 La Florida, Región Metropolitana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1297,17 +1297,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Botilleria Entre Dos Rios</t>
+          <t>Centro veterinario Italia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9 3566 0655</t>
+          <t>9 5388 2138</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Diag. Ote. 1990, 7501351 Providencia, Región Metropolitana</t>
+          <t>Rancagua 0509, 7501102 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1335,17 +1335,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Botilleria - Minimarket La Genovesa</t>
+          <t>Veterinaria London Clinic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9 7387 5107</t>
+          <t>9 7428 1836</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Seminario 197, Providencia, Región Metropolitana</t>
+          <t>dentro del condominio - Seminario 139 local 13 Torre bustamante 2, Seminario 143, Santiago, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1373,17 +1373,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Minimarket y Botilleria Arturo</t>
+          <t>Dr.Pet Clínica Veterinaria - Los Leones</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9 9265 2325</t>
+          <t>9 9887 0926</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Av. Francisco Bilbao 2946, 7510796 Providencia, Región Metropolitana</t>
+          <t>Av. Los Leones 573, 7510223 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1411,17 +1411,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LIQUIDOS.cl</t>
+          <t>Clínica Veterinaria Invet - Chile</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9 5404 5444</t>
+          <t>9 6352 6082</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Av. Providencia 2575, 7510023 Providencia, Región Metropolitana</t>
+          <t>Av. Francisco Bilbao 919, 7501098 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1449,17 +1449,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Botillería ELCHAGITO</t>
+          <t>CVI LOS LEONES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9 2011 2013</t>
+          <t>9 2637 2860</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Av. Providencia 1162, 7500000 Providencia, Región Metropolitana</t>
+          <t>Av. Los Leones 2108, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1487,17 +1487,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BOTILLERIA LOS PRIMOS</t>
+          <t>VETMONTT Petshop, alimentos, Accesorios y Peluquería de Perros Gatos</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Botilleria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9 6849 6915</t>
+          <t>9 4885 7045</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Av. Sta. Isabel 488, 7501296 Providencia, Región Metropolitana</t>
+          <t>Manuel Montt 1185, 7501050 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Casa Salvo Café</t>
+          <t>GlobAnimal Clínica y Peluquería Veterinaria</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9 5410 7550</t>
+          <t>9 6234 8757</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>General Salvo 18, Gral. Salvo 20, 7500000 Santiago, Providencia, Región Metropolitana</t>
+          <t>Av, Alférez Real 923, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1563,17 +1563,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Casa Amaranta Cafetería</t>
+          <t>Clínica Veterinaria The Cool Dogs Vet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9 4994 0126</t>
+          <t>9 8931 0165</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almte. Pastene 39, 7500535 Providencia, Región Metropolitana</t>
+          <t>Av. Los Leones 1012, 7510369 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MAI House Cafe</t>
+          <t>Club Entre Patitas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9 4010 9506</t>
+          <t>9 6123 8866</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Av. Nueva Providencia 2212, Loc 216, 7660000 Providencia, Región Metropolitana</t>
+          <t>Av. Francisco Bilbao 2419, 7510950 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1639,17 +1639,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dolce Salato Caffé</t>
+          <t>Club de Perros y Gatos Teatinos</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Veterinaria</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9 9433 3863</t>
+          <t>9 3376 2739</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Esquina - Eliodoro Yañez, Juan de Dios Vial Correa 2820, Providencia, Región Metropolitana</t>
+          <t>a pasos del Metro Santa Ana - Teatinos 490, esquina Catedral, Linea 2 del Metro, Santiago, Región Metropolitana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1677,17 +1677,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cafetería El Jardín</t>
+          <t>Mosali Boutique</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Boutique de ropa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9 8776 7444</t>
+          <t>9 9772 5841</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bellavista 368, 7520337 Providencia, Región Metropolitana</t>
+          <t>Av. Providencia 1650, Oficina 610, 7500000 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1715,17 +1715,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ciao Fiorentina</t>
+          <t>Lucky Diamonds Boutique</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Boutique de ropa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9 3868 2905</t>
+          <t>9 2814 2539</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Av. Pocuro 3015, 7510712 Providencia, Región Metropolitana</t>
+          <t>Av. Nueva Providencia, Av. Ricardo Lyon 2249, Loc 125, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Conectar Cafetería</t>
+          <t>Alma Regia Boutique</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Boutique de ropa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9 9211 9590</t>
+          <t>9 2814 2539</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Av. Providencia 215, 7500000 Providencia, Región Metropolitana</t>
+          <t>Av. Nueva Providencia, Av. Ricardo Lyon 2249, Loc 125, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1791,17 +1791,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mikkas Coffee</t>
+          <t>The Ocean Store</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Boutique de ropa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9 6758 0357</t>
+          <t>9 5092 1827</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sta. Magdalena 41, Loc 1, 7500000 Providencia, Región Metropolitana</t>
+          <t>21, Av. Providencia 1336, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1829,17 +1829,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Santa Cafeina</t>
+          <t>Mariagustina Diseños</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Boutique de ropa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9 7905 4662</t>
+          <t>9 5092 1827</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Av. Providencia 2471, 7500000 Providencia, Región Metropolitana</t>
+          <t>21, Av. Providencia 1336, Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1867,17 +1867,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Selva Cafetería</t>
+          <t>Kadenkas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cafeteria</t>
+          <t>Boutique de ropa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9 8809 4267</t>
+          <t>9 8732 7208</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monseñor Miller 22b, Providencia, Región Metropolitana</t>
+          <t>Av. Providencia 2601, Loc 38, 7510015 Providencia, Región Metropolitana</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1901,6 +1901,2020 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>La Coquetería Boutique</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Boutique de ropa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>9 8732 7208</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Av. Providencia 2601, Loc 38, 7510015 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Calper - Uniformes Clínicos Providencia Santiago</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Boutique de ropa</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>9 3187 4111</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Antonio Varas 299, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TIENDA KIARA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Boutique de ropa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9 5676 2004</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Av. Italia 1380, 7501451 Santiago, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>UNIKS SPA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Boutique de ropa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9 3559 2096</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Av. Nueva Providencia 2160, Loc 64, 7510121 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Salón de Belleza Veranvior</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>9 5200 0003</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Coll y Pi 124 b, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Pelos sa</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>9 5200 0003</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Coll y Pi 124 b, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Peluquería TIS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>9 5200 0003</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Coll y Pi 124 b, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Salon Corazón de Pelo</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>9 6366 6776</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Seminario 252, 7501269 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LATELIER DELUXE Salón de Belleza</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>9 5416 7235</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Padre Mariano 10, local 4, 7500495 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dani Arriagada Salón Providencia</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>9 9824 6366</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Eliodoro Yáñez 869, 7500683 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ROSS ART</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>9 5835 1854</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Av. Salvador 1333, 7501358 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PELUQUERÍA Elvi_estilista</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>9 5127 5381</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Girardi 1356, 7501454 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>El Otro Sebastian - La Peluquería</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>9 7733 4820</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Av. Sta. María 2318, 7520426 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RR Salon de Belleza</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Peluqueria</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>9 5380 5724</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Padre Mariano 430, 8320000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Barbería TIS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>9 3591 4806</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Condell 1380, 7501463 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Barberia The Gold Two</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>9 3591 4806</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Condell 1380, 7501463 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>La Barbería</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>9 8975 0668</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Condell 1166, Loc 104, 7501294 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Barberia Providencia Master look</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>9 4912 4645</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Av. Nueva Providencia 1945, Oficina 14-08, 7500503 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BARBER STUDIO PROVIDENCIA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>9 5856 5781</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Eliodoro Yáñez 1118, 7500605 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Barber Kingz</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>9 4056 2128</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Galería La Fuente - Av. Providencia 2550, Loc 27, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Barbería O-D-7 Providencia</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>9 2936 7193</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Av. Providencia 1998, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Suecia BarberShop</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>9 5414 9319</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Av. Nueva Providencia 2327, 7510096 Santiago, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Barbudos Barberia</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Barberia</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>9 3062 4045</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Avenida Nueva Providencia 2260 Local, 102 Piso2, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Estetica Providencia</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>9 4592 9361</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Av. Providencia 2230, Ofi C53, Santiago, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Aurora Estética - Centro de belleza y Estética</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>9 4592 9361</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Av. Providencia 2230, Ofi C53, Santiago, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Clínica EM Estétika Médica, Providencia</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>44 222 9928</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Vieja - Guardia Vieja 202, Of.301, 7510188 Santiago, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Clemistica Beauty Spa</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>9 2908 5965</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Manuel Montt 252, Oficina 216, 7500591 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Centro de Estética NCA - Guardia Vieja</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>9 9078 4304</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Guardia Vieja 255, Ofi 1506, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AKALI Centro de estética</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>9 4030 1706</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Av. Salvador 95, Ofi 510, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CB Medicina Estética Providencia Cara Bonita Rinomodelación Botox Sculptra Mesoterapia Exosomas</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>9 3100 7002</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Av. Luis Thayer Ojeda 236, Ofi 61, 7510068 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Clínica Bela</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>9 3100 7002</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Av. Luis Thayer Ojeda 236, Ofi 61, 7510068 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Clínica Be Now</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>9 3077 8917</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Fidel Oteiza 1921, Ofi 601, 7500523 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estetica De Chile</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Centro de estetica</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>9 3077 8917</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fidel Oteiza 1921, Ofi 601, 7500523 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Distribuidora Bartom</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>9 6376 1258</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Av. Providencia 1017, 7500620 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Distribuidora Lastarria</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>9 8269 1417</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Avenida Providencia 1100 Local, 7A Interior, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>La Popular Alimentos</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>9 4939 2851</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Rancagua 0167, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Distribuidora David Granada</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>9 6145 2486</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>edificio copiapo - Av. Hernando de Aguirre 128, Ofi 403, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Productos Congelados Providencia DEL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>9 7862 6212</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Av. Pedro de Valdivia 247, 7500524 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sexshop Mayorista</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>9 7974 9341</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Av. Nueva Providencia 1745, Loc G, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Distribuidora Santiago</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>9 7570 9867</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Juan Martínez de Rozas 3047, Santiago, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Distribuidora Surtiventas</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>9 8696 8657</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Av. Nueva Providencia 1881 1809, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LIQUIDOS.cl</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>9 8669 4821</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Av. Francisco Bilbao 1097, Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA DE HUEVOS PANCHITA</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>9 3330 1901</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Emilio Vaisse 522, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CIDENTAL - Clínica Dental</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>9 7268 0884</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Rancagua 089, 7501180 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Clinica Dental Providencia Dra Pilar Angel</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>9 7672 8977</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Dr. Manuel Barros Borgoño 110, Ofi 0104, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Dentista, Clínica Dental CEOS - Providencia</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>9 4497 9077</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Av. Salvador 95, Oficina 507, 7500710 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Clinica Dental La Providencia</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>9 7316 5751</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Gral del Canto 105, 7500589 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SVG Clínica Dental Providencia</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>9 8550 1250</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Av. Luis Thayer Ojeda 0130, Ofi 401, 7510001 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Clínica Dental Tajamar</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>9 3866 8643</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Av. Providencia 1100, Loc 44, 7500000 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Orthoplan Providencia - clínica dental</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>9 3861 3869</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>María Luisa Santander 468, 7500833 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CLÍNICA ODONTOLÓGICA BOCA A BOCA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>9 5358 0117</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Av. Providencia 1650, Ofi 311, 7500027 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Clínica Odontológica Smartdent Providencia</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>800 362 232</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Fidel Oteiza 1971, 7500522 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Clínica Aires Clínica Dental en Providencia</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Clinica dental</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>9 8426 4990</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Av. Nueva Providencia 2214, Of. 59, 7510086 Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
